--- a/data/trans_orig/IP07_C15_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C15_2023-Edad-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han producido situaciones de cyberbulling fuera de su colegio en 2023 (tasa de respuesta: 92,89%)</t>
+          <t>Menores según si se han producido situaciones de cyberbulling fuera de su colegio/instituto en 2023 (tasa de respuesta: 92,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8677</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4427</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14049</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,46%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15,32%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5549</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2581</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10126</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,36%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14583</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14752</t>
+          <t>14581</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8899</t>
+          <t>9450</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>22320</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>83036</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>77664</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>87286</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,54%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>84,68%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,17%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>60376</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>55799</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>63344</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>91,58%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,64%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,09%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>83161</t>
+          <t>63643</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77780</t>
+          <t>58505</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87307</t>
+          <t>66744</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>143536</t>
+          <t>146679</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136391</t>
+          <t>138940</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149389</t>
+          <t>151810</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>91713</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>91713</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>91713</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>65925</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>65925</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>65925</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>92363</t>
+          <t>69547</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>92363</t>
+          <t>69547</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>92363</t>
+          <t>69547</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>158288</t>
+          <t>161260</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>158288</t>
+          <t>161260</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>158288</t>
+          <t>161260</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17788</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11045</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27296</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,35%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,42%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>15710</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7764</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24618</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11,82%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18,53%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19172</t>
+          <t>16041</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>10630</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29181</t>
+          <t>23009</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>34882</t>
+          <t>33829</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23342</t>
+          <t>24747</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47307</t>
+          <t>46416</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>138881</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>129373</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>145624</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>88,65%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,95%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>117160</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>108252</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>125106</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>88,18%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>81,47%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,16%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>138848</t>
+          <t>99813</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>128839</t>
+          <t>92845</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>146576</t>
+          <t>105224</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>256008</t>
+          <t>238694</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>243583</t>
+          <t>226107</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>267548</t>
+          <t>247776</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>90,92%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156669</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156669</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156669</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>132870</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>132870</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>132870</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>158020</t>
+          <t>115854</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>158020</t>
+          <t>115854</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>158020</t>
+          <t>115854</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>290890</t>
+          <t>272523</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>290890</t>
+          <t>272523</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>290890</t>
+          <t>272523</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>26465</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18627</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>37449</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,5%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,08%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>21260</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11854</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>30319</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,69%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,25%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28374</t>
+          <t>21944</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19212</t>
+          <t>15458</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40210</t>
+          <t>30076</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>49633</t>
+          <t>48409</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36702</t>
+          <t>37331</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63756</t>
+          <t>60644</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>221917</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>210933</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>229755</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,35%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,92%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,5%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>177535</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>168476</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>186941</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>89,31%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,75%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,04%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>222009</t>
+          <t>163457</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>210173</t>
+          <t>155325</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>231171</t>
+          <t>169943</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>399545</t>
+          <t>385374</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>385422</t>
+          <t>373139</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>412476</t>
+          <t>396452</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>248382</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>248382</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>248382</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>198795</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>198795</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>198795</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>250383</t>
+          <t>185401</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>250383</t>
+          <t>185401</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>250383</t>
+          <t>185401</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>449178</t>
+          <t>433783</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>449178</t>
+          <t>433783</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>449178</t>
+          <t>433783</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
